--- a/database/controller_excel/Resguardo_Edgar_Miranda.xlsx
+++ b/database/controller_excel/Resguardo_Edgar_Miranda.xlsx
@@ -95,7 +95,7 @@
     <t>MXL4372XC4</t>
   </si>
   <si>
-    <t>dsada</t>
+    <t>czcsad</t>
   </si>
   <si>
     <t>DVZ-VH-TI-00138</t>
@@ -287,7 +287,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="true">
       <protection locked="true" hidden="false"/>
     </xf>
@@ -429,6 +429,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="true">
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -969,27 +973,27 @@
       <c r="I18" s="22"/>
     </row>
     <row r="19" spans="1:10" customHeight="1" ht="15">
-      <c r="A19" s="22">
+      <c r="A19" s="38">
         <v>1</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="D19" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22" t="s">
+      <c r="E19" s="38"/>
+      <c r="F19" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22" t="s">
+      <c r="G19" s="38"/>
+      <c r="H19" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="I19" s="22"/>
+      <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="15">
       <c r="A20" s="22"/>
@@ -1005,46 +1009,46 @@
       <c r="I20" s="22"/>
     </row>
     <row r="21" spans="1:10" customHeight="1" ht="15">
-      <c r="A21" s="22">
+      <c r="A21" s="38">
         <v>2</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22" t="s">
+      <c r="E21" s="38"/>
+      <c r="F21" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
     </row>
     <row r="22" spans="1:10" customHeight="1" ht="15">
-      <c r="A22" s="22">
+      <c r="A22" s="38">
         <v>3</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22" t="s">
+      <c r="E22" s="38"/>
+      <c r="F22" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
     </row>
     <row r="23" spans="1:10" customHeight="1" ht="15">
       <c r="A23" s="16"/>
